--- a/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
+++ b/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:51:45+00:00</t>
+    <t>2026-02-03T14:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
+++ b/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T14:58:38+00:00</t>
+    <t>2026-02-17T13:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
+++ b/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:17:39+00:00</t>
+    <t>2026-02-17T14:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
+++ b/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:34:23+00:00</t>
+    <t>2026-02-22T17:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
+++ b/nr-valueset-ruleset/ig/StructureDefinition-fr-core-organization-champ-activite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:13:24+00:00</t>
+    <t>2026-02-22T17:25:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
